--- a/backend/scripts/audit-output/expeditor-smoke/ex-5.1.3.xlsx
+++ b/backend/scripts/audit-output/expeditor-smoke/ex-5.1.3.xlsx
@@ -14,9 +14,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="119">
-  <si>
-    <t>Загрузочный лист 5.1.3 (Время печати: 27.05.2026 19:51:40)</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="119">
+  <si>
+    <t>Загрузочный лист 5.1.3 (Время печати: 28.05.2026 17:37:19)</t>
   </si>
   <si>
     <t>Бисёр Маркэт</t>
@@ -902,7 +902,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
   <dimension ref="A1:AQ45"/>
-  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
     <col min="2" max="2" width="15" customWidth="1"/>
@@ -1415,9 +1415,7 @@
       </c>
       <c r="C8" s="12"/>
       <c r="D8" s="13"/>
-      <c r="E8" s="13">
-        <v>648</v>
-      </c>
+      <c r="E8" s="13"/>
       <c r="F8" s="13"/>
       <c r="G8" s="13"/>
       <c r="H8" s="13"/>
@@ -1503,9 +1501,7 @@
       <c r="AK9" s="3"/>
       <c r="AL9" s="3"/>
       <c r="AM9" s="3"/>
-      <c r="AN9" s="3">
-        <v>5</v>
-      </c>
+      <c r="AN9" s="3"/>
       <c r="AO9" s="3"/>
       <c r="AP9" s="3"/>
       <c r="AQ9" s="3"/>
@@ -1556,9 +1552,7 @@
       <c r="AK10" s="3"/>
       <c r="AL10" s="3"/>
       <c r="AM10" s="3"/>
-      <c r="AN10" s="3">
-        <v>3</v>
-      </c>
+      <c r="AN10" s="3"/>
       <c r="AO10" s="3"/>
       <c r="AP10" s="3"/>
       <c r="AQ10" s="3"/>
@@ -1579,9 +1573,7 @@
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
       <c r="I11" s="3"/>
-      <c r="J11" s="3">
-        <v>1</v>
-      </c>
+      <c r="J11" s="3"/>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
@@ -1629,20 +1621,12 @@
       </c>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
-      <c r="G12" s="3">
-        <v>6</v>
-      </c>
+      <c r="G12" s="3"/>
       <c r="H12" s="3"/>
       <c r="I12" s="3"/>
-      <c r="J12" s="3">
-        <v>1</v>
-      </c>
-      <c r="K12" s="3">
-        <v>4</v>
-      </c>
-      <c r="L12" s="3">
-        <v>3</v>
-      </c>
+      <c r="J12" s="3"/>
+      <c r="K12" s="3"/>
+      <c r="L12" s="3"/>
       <c r="M12" s="3"/>
       <c r="N12" s="3"/>
       <c r="O12" s="3"/>
@@ -1652,9 +1636,7 @@
       <c r="S12" s="3"/>
       <c r="T12" s="3"/>
       <c r="U12" s="3"/>
-      <c r="V12" s="3">
-        <v>3</v>
-      </c>
+      <c r="V12" s="3"/>
       <c r="W12" s="3"/>
       <c r="X12" s="3"/>
       <c r="Y12" s="3"/>
@@ -1672,9 +1654,7 @@
       <c r="AK12" s="3"/>
       <c r="AL12" s="3"/>
       <c r="AM12" s="3"/>
-      <c r="AN12" s="3">
-        <v>6</v>
-      </c>
+      <c r="AN12" s="3"/>
       <c r="AO12" s="3"/>
       <c r="AP12" s="3"/>
       <c r="AQ12" s="3"/>
@@ -1695,13 +1675,9 @@
       <c r="G13" s="3"/>
       <c r="H13" s="3"/>
       <c r="I13" s="3"/>
-      <c r="J13" s="3">
-        <v>1</v>
-      </c>
+      <c r="J13" s="3"/>
       <c r="K13" s="3"/>
-      <c r="L13" s="3">
-        <v>3</v>
-      </c>
+      <c r="L13" s="3"/>
       <c r="M13" s="3"/>
       <c r="N13" s="3"/>
       <c r="O13" s="3"/>
@@ -1711,9 +1687,7 @@
       <c r="S13" s="3"/>
       <c r="T13" s="3"/>
       <c r="U13" s="3"/>
-      <c r="V13" s="3">
-        <v>3</v>
-      </c>
+      <c r="V13" s="3"/>
       <c r="W13" s="3"/>
       <c r="X13" s="3"/>
       <c r="Y13" s="3"/>
@@ -1731,9 +1705,7 @@
       <c r="AK13" s="3"/>
       <c r="AL13" s="3"/>
       <c r="AM13" s="3"/>
-      <c r="AN13" s="3">
-        <v>6</v>
-      </c>
+      <c r="AN13" s="3"/>
       <c r="AO13" s="3"/>
       <c r="AP13" s="3"/>
       <c r="AQ13" s="3"/>
@@ -1745,9 +1717,7 @@
       </c>
       <c r="C14" s="12"/>
       <c r="D14" s="13"/>
-      <c r="E14" s="13">
-        <v>14</v>
-      </c>
+      <c r="E14" s="13"/>
       <c r="F14" s="13"/>
       <c r="G14" s="13"/>
       <c r="H14" s="13"/>
@@ -1813,12 +1783,8 @@
       <c r="Q15" s="3"/>
       <c r="R15" s="3"/>
       <c r="S15" s="3"/>
-      <c r="T15" s="3">
-        <v>2</v>
-      </c>
-      <c r="U15" s="3">
-        <v>3</v>
-      </c>
+      <c r="T15" s="3"/>
+      <c r="U15" s="3"/>
       <c r="V15" s="3"/>
       <c r="W15" s="3"/>
       <c r="X15" s="3"/>
@@ -1859,9 +1825,7 @@
       <c r="H16" s="3"/>
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
-      <c r="K16" s="3">
-        <v>2</v>
-      </c>
+      <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
@@ -1870,12 +1834,8 @@
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
-      <c r="T16" s="3">
-        <v>2</v>
-      </c>
-      <c r="U16" s="3">
-        <v>1</v>
-      </c>
+      <c r="T16" s="3"/>
+      <c r="U16" s="3"/>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
@@ -1883,9 +1843,7 @@
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
-      <c r="AC16" s="3">
-        <v>4</v>
-      </c>
+      <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
@@ -1908,9 +1866,7 @@
       </c>
       <c r="C17" s="12"/>
       <c r="D17" s="13"/>
-      <c r="E17" s="13">
-        <v>3990</v>
-      </c>
+      <c r="E17" s="13"/>
       <c r="F17" s="13"/>
       <c r="G17" s="13"/>
       <c r="H17" s="13"/>
@@ -1969,9 +1925,7 @@
       <c r="J18" s="3"/>
       <c r="K18" s="3"/>
       <c r="L18" s="3"/>
-      <c r="M18" s="3">
-        <v>15</v>
-      </c>
+      <c r="M18" s="3"/>
       <c r="N18" s="3"/>
       <c r="O18" s="3"/>
       <c r="P18" s="3"/>
@@ -1981,35 +1935,25 @@
       <c r="T18" s="3"/>
       <c r="U18" s="3"/>
       <c r="V18" s="3"/>
-      <c r="W18" s="3">
-        <v>6</v>
-      </c>
+      <c r="W18" s="3"/>
       <c r="X18" s="3"/>
       <c r="Y18" s="3"/>
       <c r="Z18" s="3"/>
       <c r="AA18" s="3"/>
       <c r="AB18" s="3"/>
       <c r="AC18" s="3"/>
-      <c r="AD18" s="3">
-        <v>15</v>
-      </c>
+      <c r="AD18" s="3"/>
       <c r="AE18" s="3"/>
       <c r="AF18" s="3"/>
-      <c r="AG18" s="3">
-        <v>9</v>
-      </c>
+      <c r="AG18" s="3"/>
       <c r="AH18" s="3"/>
       <c r="AI18" s="3"/>
-      <c r="AJ18" s="3">
-        <v>12</v>
-      </c>
+      <c r="AJ18" s="3"/>
       <c r="AK18" s="3"/>
       <c r="AL18" s="3"/>
       <c r="AM18" s="3"/>
       <c r="AN18" s="3"/>
-      <c r="AO18" s="3">
-        <v>9</v>
-      </c>
+      <c r="AO18" s="3"/>
       <c r="AP18" s="3"/>
       <c r="AQ18" s="3"/>
     </row>
@@ -2037,9 +1981,7 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-      <c r="R19" s="3">
-        <v>24</v>
-      </c>
+      <c r="R19" s="3"/>
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
@@ -2078,90 +2020,42 @@
         <v>12900</v>
       </c>
       <c r="E20" s="3"/>
-      <c r="F20" s="3">
-        <v>12</v>
-      </c>
+      <c r="F20" s="3"/>
       <c r="G20" s="3"/>
-      <c r="H20" s="3">
-        <v>15</v>
-      </c>
-      <c r="I20" s="3">
-        <v>30</v>
-      </c>
+      <c r="H20" s="3"/>
+      <c r="I20" s="3"/>
       <c r="J20" s="3"/>
       <c r="K20" s="3"/>
-      <c r="L20" s="3">
-        <v>6</v>
-      </c>
+      <c r="L20" s="3"/>
       <c r="M20" s="3"/>
       <c r="N20" s="3"/>
-      <c r="O20" s="3">
-        <v>9</v>
-      </c>
+      <c r="O20" s="3"/>
       <c r="P20" s="3"/>
-      <c r="Q20" s="3">
-        <v>12</v>
-      </c>
-      <c r="R20" s="3">
-        <v>24</v>
-      </c>
-      <c r="S20" s="3">
-        <v>12</v>
-      </c>
-      <c r="T20" s="3">
-        <v>15</v>
-      </c>
-      <c r="U20" s="3">
-        <v>12</v>
-      </c>
+      <c r="Q20" s="3"/>
+      <c r="R20" s="3"/>
+      <c r="S20" s="3"/>
+      <c r="T20" s="3"/>
+      <c r="U20" s="3"/>
       <c r="V20" s="3"/>
-      <c r="W20" s="3">
-        <v>6</v>
-      </c>
+      <c r="W20" s="3"/>
       <c r="X20" s="3"/>
-      <c r="Y20" s="3">
-        <v>15</v>
-      </c>
-      <c r="Z20" s="3">
-        <v>12</v>
-      </c>
-      <c r="AA20" s="3">
-        <v>15</v>
-      </c>
-      <c r="AB20" s="3">
-        <v>21</v>
-      </c>
+      <c r="Y20" s="3"/>
+      <c r="Z20" s="3"/>
+      <c r="AA20" s="3"/>
+      <c r="AB20" s="3"/>
       <c r="AC20" s="3"/>
       <c r="AD20" s="3"/>
-      <c r="AE20" s="3">
-        <v>9</v>
-      </c>
-      <c r="AF20" s="3">
-        <v>6</v>
-      </c>
-      <c r="AG20" s="3">
-        <v>9</v>
-      </c>
-      <c r="AH20" s="3">
-        <v>15</v>
-      </c>
-      <c r="AI20" s="3">
-        <v>60</v>
-      </c>
+      <c r="AE20" s="3"/>
+      <c r="AF20" s="3"/>
+      <c r="AG20" s="3"/>
+      <c r="AH20" s="3"/>
+      <c r="AI20" s="3"/>
       <c r="AJ20" s="3"/>
-      <c r="AK20" s="3">
-        <v>6</v>
-      </c>
-      <c r="AL20" s="3">
-        <v>15</v>
-      </c>
-      <c r="AM20" s="3">
-        <v>30</v>
-      </c>
+      <c r="AK20" s="3"/>
+      <c r="AL20" s="3"/>
+      <c r="AM20" s="3"/>
       <c r="AN20" s="3"/>
-      <c r="AO20" s="3">
-        <v>9</v>
-      </c>
+      <c r="AO20" s="3"/>
       <c r="AP20" s="3"/>
       <c r="AQ20" s="3"/>
     </row>
@@ -2172,9 +2066,7 @@
       </c>
       <c r="C21" s="12"/>
       <c r="D21" s="13"/>
-      <c r="E21" s="13">
-        <v>0</v>
-      </c>
+      <c r="E21" s="13"/>
       <c r="F21" s="13"/>
       <c r="G21" s="13"/>
       <c r="H21" s="13"/>
@@ -2232,15 +2124,11 @@
       <c r="I22" s="3"/>
       <c r="J22" s="3"/>
       <c r="K22" s="3"/>
-      <c r="L22" s="3">
-        <v>4</v>
-      </c>
+      <c r="L22" s="3"/>
       <c r="M22" s="3"/>
       <c r="N22" s="3"/>
       <c r="O22" s="3"/>
-      <c r="P22" s="3">
-        <v>24</v>
-      </c>
+      <c r="P22" s="3"/>
       <c r="Q22" s="3"/>
       <c r="R22" s="3"/>
       <c r="S22" s="3"/>
@@ -2248,16 +2136,12 @@
       <c r="U22" s="3"/>
       <c r="V22" s="3"/>
       <c r="W22" s="3"/>
-      <c r="X22" s="3">
-        <v>3</v>
-      </c>
+      <c r="X22" s="3"/>
       <c r="Y22" s="3"/>
       <c r="Z22" s="3"/>
       <c r="AA22" s="3"/>
       <c r="AB22" s="3"/>
-      <c r="AC22" s="3">
-        <v>12</v>
-      </c>
+      <c r="AC22" s="3"/>
       <c r="AD22" s="3"/>
       <c r="AE22" s="3"/>
       <c r="AF22" s="3"/>
@@ -2291,15 +2175,11 @@
       <c r="I23" s="3"/>
       <c r="J23" s="3"/>
       <c r="K23" s="3"/>
-      <c r="L23" s="3">
-        <v>4</v>
-      </c>
+      <c r="L23" s="3"/>
       <c r="M23" s="3"/>
       <c r="N23" s="3"/>
       <c r="O23" s="3"/>
-      <c r="P23" s="3">
-        <v>48</v>
-      </c>
+      <c r="P23" s="3"/>
       <c r="Q23" s="3"/>
       <c r="R23" s="3"/>
       <c r="S23" s="3"/>
@@ -2307,9 +2187,7 @@
       <c r="U23" s="3"/>
       <c r="V23" s="3"/>
       <c r="W23" s="3"/>
-      <c r="X23" s="3">
-        <v>3</v>
-      </c>
+      <c r="X23" s="3"/>
       <c r="Y23" s="3"/>
       <c r="Z23" s="3"/>
       <c r="AA23" s="3"/>
@@ -2352,9 +2230,7 @@
       <c r="M24" s="3"/>
       <c r="N24" s="3"/>
       <c r="O24" s="3"/>
-      <c r="P24" s="3">
-        <v>25</v>
-      </c>
+      <c r="P24" s="3"/>
       <c r="Q24" s="3"/>
       <c r="R24" s="3"/>
       <c r="S24" s="3"/>
@@ -2405,20 +2281,14 @@
       <c r="M25" s="3"/>
       <c r="N25" s="3"/>
       <c r="O25" s="3"/>
-      <c r="P25" s="3">
-        <v>50</v>
-      </c>
-      <c r="Q25" s="3">
-        <v>5</v>
-      </c>
+      <c r="P25" s="3"/>
+      <c r="Q25" s="3"/>
       <c r="R25" s="3"/>
       <c r="S25" s="3"/>
       <c r="T25" s="3"/>
       <c r="U25" s="3"/>
       <c r="V25" s="3"/>
-      <c r="W25" s="3">
-        <v>5</v>
-      </c>
+      <c r="W25" s="3"/>
       <c r="X25" s="3"/>
       <c r="Y25" s="3"/>
       <c r="Z25" s="3"/>
@@ -2447,9 +2317,7 @@
       </c>
       <c r="C26" s="12"/>
       <c r="D26" s="13"/>
-      <c r="E26" s="13">
-        <v>32</v>
-      </c>
+      <c r="E26" s="13"/>
       <c r="F26" s="13"/>
       <c r="G26" s="13"/>
       <c r="H26" s="13"/>
@@ -2538,9 +2406,7 @@
       <c r="AN27" s="3"/>
       <c r="AO27" s="3"/>
       <c r="AP27" s="3"/>
-      <c r="AQ27" s="3">
-        <v>32</v>
-      </c>
+      <c r="AQ27" s="3"/>
     </row>
     <row r="28" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A28" s="3"/>
@@ -2613,9 +2479,7 @@
       <c r="Q29" s="3"/>
       <c r="R29" s="3"/>
       <c r="S29" s="3"/>
-      <c r="T29" s="3">
-        <v>1</v>
-      </c>
+      <c r="T29" s="3"/>
       <c r="U29" s="3"/>
       <c r="V29" s="3"/>
       <c r="W29" s="3"/>
@@ -2624,9 +2488,7 @@
       <c r="Z29" s="3"/>
       <c r="AA29" s="3"/>
       <c r="AB29" s="3"/>
-      <c r="AC29" s="3">
-        <v>1</v>
-      </c>
+      <c r="AC29" s="3"/>
       <c r="AD29" s="3"/>
       <c r="AE29" s="3"/>
       <c r="AF29" s="3"/>
@@ -2667,9 +2529,7 @@
       <c r="R30" s="3"/>
       <c r="S30" s="3"/>
       <c r="T30" s="3"/>
-      <c r="U30" s="3">
-        <v>1</v>
-      </c>
+      <c r="U30" s="3"/>
       <c r="V30" s="3"/>
       <c r="W30" s="3"/>
       <c r="X30" s="3"/>
@@ -2703,90 +2563,42 @@
       <c r="C31" s="4"/>
       <c r="D31" s="3"/>
       <c r="E31" s="3"/>
-      <c r="F31" s="3">
-        <v>4</v>
-      </c>
+      <c r="F31" s="3"/>
       <c r="G31" s="3"/>
-      <c r="H31" s="3">
-        <v>5</v>
-      </c>
-      <c r="I31" s="3">
-        <v>10</v>
-      </c>
+      <c r="H31" s="3"/>
+      <c r="I31" s="3"/>
       <c r="J31" s="3"/>
       <c r="K31" s="3"/>
-      <c r="L31" s="3">
-        <v>2</v>
-      </c>
+      <c r="L31" s="3"/>
       <c r="M31" s="3"/>
       <c r="N31" s="3"/>
-      <c r="O31" s="3">
-        <v>3</v>
-      </c>
+      <c r="O31" s="3"/>
       <c r="P31" s="3"/>
-      <c r="Q31" s="3">
-        <v>4</v>
-      </c>
-      <c r="R31" s="3">
-        <v>16</v>
-      </c>
-      <c r="S31" s="3">
-        <v>4</v>
-      </c>
-      <c r="T31" s="3">
-        <v>5</v>
-      </c>
-      <c r="U31" s="3">
-        <v>4</v>
-      </c>
+      <c r="Q31" s="3"/>
+      <c r="R31" s="3"/>
+      <c r="S31" s="3"/>
+      <c r="T31" s="3"/>
+      <c r="U31" s="3"/>
       <c r="V31" s="3"/>
-      <c r="W31" s="3">
-        <v>2</v>
-      </c>
+      <c r="W31" s="3"/>
       <c r="X31" s="3"/>
-      <c r="Y31" s="3">
-        <v>5</v>
-      </c>
-      <c r="Z31" s="3">
-        <v>4</v>
-      </c>
-      <c r="AA31" s="3">
-        <v>5</v>
-      </c>
-      <c r="AB31" s="3">
-        <v>7</v>
-      </c>
+      <c r="Y31" s="3"/>
+      <c r="Z31" s="3"/>
+      <c r="AA31" s="3"/>
+      <c r="AB31" s="3"/>
       <c r="AC31" s="3"/>
       <c r="AD31" s="3"/>
-      <c r="AE31" s="3">
-        <v>3</v>
-      </c>
-      <c r="AF31" s="3">
-        <v>2</v>
-      </c>
-      <c r="AG31" s="3">
-        <v>3</v>
-      </c>
-      <c r="AH31" s="3">
-        <v>5</v>
-      </c>
-      <c r="AI31" s="3">
-        <v>20</v>
-      </c>
+      <c r="AE31" s="3"/>
+      <c r="AF31" s="3"/>
+      <c r="AG31" s="3"/>
+      <c r="AH31" s="3"/>
+      <c r="AI31" s="3"/>
       <c r="AJ31" s="3"/>
-      <c r="AK31" s="3">
-        <v>2</v>
-      </c>
-      <c r="AL31" s="3">
-        <v>5</v>
-      </c>
-      <c r="AM31" s="3">
-        <v>10</v>
-      </c>
+      <c r="AK31" s="3"/>
+      <c r="AL31" s="3"/>
+      <c r="AM31" s="3"/>
       <c r="AN31" s="3"/>
-      <c r="AO31" s="3">
-        <v>3</v>
-      </c>
+      <c r="AO31" s="3"/>
       <c r="AP31" s="3"/>
       <c r="AQ31" s="3"/>
     </row>
@@ -2797,7 +2609,9 @@
       </c>
       <c r="C32" s="4"/>
       <c r="D32" s="3"/>
-      <c r="E32" s="17"/>
+      <c r="E32" s="17">
+        <v>6017</v>
+      </c>
       <c r="F32" s="17">
         <v>16</v>
       </c>
@@ -2922,7 +2736,9 @@
       <c r="D33" s="21" t="s">
         <v>114</v>
       </c>
-      <c r="E33" s="22"/>
+      <c r="E33" s="22">
+        <v>11676900</v>
+      </c>
       <c r="F33" s="21">
         <v>154800</v>
       </c>
@@ -3096,9 +2912,7 @@
       <c r="H35" s="3"/>
       <c r="I35" s="3"/>
       <c r="J35" s="3"/>
-      <c r="K35" s="3">
-        <v>2</v>
-      </c>
+      <c r="K35" s="3"/>
       <c r="L35" s="3"/>
       <c r="M35" s="3"/>
       <c r="N35" s="3"/>
@@ -3129,9 +2943,7 @@
       <c r="AM35" s="3"/>
       <c r="AN35" s="3"/>
       <c r="AO35" s="3"/>
-      <c r="AP35" s="3">
-        <v>2</v>
-      </c>
+      <c r="AP35" s="3"/>
       <c r="AQ35" s="3"/>
     </row>
     <row r="36" spans="1:43" x14ac:dyDescent="0.25">
@@ -3180,9 +2992,7 @@
       <c r="AM36" s="3"/>
       <c r="AN36" s="3"/>
       <c r="AO36" s="3"/>
-      <c r="AP36" s="3">
-        <v>1</v>
-      </c>
+      <c r="AP36" s="3"/>
       <c r="AQ36" s="3"/>
     </row>
     <row r="37" spans="1:43" x14ac:dyDescent="0.25">
@@ -3231,9 +3041,7 @@
       <c r="AM37" s="3"/>
       <c r="AN37" s="3"/>
       <c r="AO37" s="3"/>
-      <c r="AP37" s="3">
-        <v>2</v>
-      </c>
+      <c r="AP37" s="3"/>
       <c r="AQ37" s="3"/>
     </row>
     <row r="38" spans="1:43" x14ac:dyDescent="0.25">
@@ -3282,9 +3090,7 @@
       <c r="AM38" s="3"/>
       <c r="AN38" s="3"/>
       <c r="AO38" s="3"/>
-      <c r="AP38" s="3">
-        <v>1</v>
-      </c>
+      <c r="AP38" s="3"/>
       <c r="AQ38" s="3"/>
     </row>
     <row r="39" spans="1:43" x14ac:dyDescent="0.25">
@@ -3333,9 +3139,7 @@
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
-      <c r="AP39" s="3">
-        <v>19</v>
-      </c>
+      <c r="AP39" s="3"/>
       <c r="AQ39" s="3"/>
     </row>
     <row r="40" spans="1:43" x14ac:dyDescent="0.25">
@@ -3384,9 +3188,7 @@
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
-      <c r="AP40" s="3">
-        <v>2</v>
-      </c>
+      <c r="AP40" s="3"/>
       <c r="AQ40" s="3"/>
     </row>
     <row r="41" spans="1:43" x14ac:dyDescent="0.25">
@@ -3435,9 +3237,7 @@
       <c r="AM41" s="3"/>
       <c r="AN41" s="3"/>
       <c r="AO41" s="3"/>
-      <c r="AP41" s="3">
-        <v>2</v>
-      </c>
+      <c r="AP41" s="3"/>
       <c r="AQ41" s="3"/>
     </row>
     <row r="42" spans="1:43" x14ac:dyDescent="0.25">
@@ -3486,9 +3286,7 @@
       <c r="AM42" s="3"/>
       <c r="AN42" s="3"/>
       <c r="AO42" s="3"/>
-      <c r="AP42" s="3">
-        <v>1</v>
-      </c>
+      <c r="AP42" s="3"/>
       <c r="AQ42" s="3"/>
     </row>
     <row r="43" spans="1:43" x14ac:dyDescent="0.25">
@@ -3537,9 +3335,7 @@
       <c r="AM43" s="3"/>
       <c r="AN43" s="3"/>
       <c r="AO43" s="3"/>
-      <c r="AP43" s="3">
-        <v>1</v>
-      </c>
+      <c r="AP43" s="3"/>
       <c r="AQ43" s="3"/>
     </row>
     <row r="44" spans="1:43" x14ac:dyDescent="0.25">
@@ -3557,14 +3353,10 @@
       <c r="H44" s="3"/>
       <c r="I44" s="3"/>
       <c r="J44" s="3"/>
-      <c r="K44" s="3">
-        <v>1</v>
-      </c>
+      <c r="K44" s="3"/>
       <c r="L44" s="3"/>
       <c r="M44" s="3"/>
-      <c r="N44" s="3">
-        <v>20</v>
-      </c>
+      <c r="N44" s="3"/>
       <c r="O44" s="3"/>
       <c r="P44" s="3"/>
       <c r="Q44" s="3"/>
@@ -3613,9 +3405,7 @@
       <c r="K45" s="3"/>
       <c r="L45" s="3"/>
       <c r="M45" s="3"/>
-      <c r="N45" s="3">
-        <v>60</v>
-      </c>
+      <c r="N45" s="3"/>
       <c r="O45" s="3"/>
       <c r="P45" s="3"/>
       <c r="Q45" s="3"/>
@@ -3739,6 +3529,6 @@
     <mergeCell ref="B45:C45"/>
   </mergeCells>
   <pageMargins left="0.2" right="0.2" top="0.2" bottom="0.2" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="default" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup paperSize="9" orientation="portrait" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>